--- a/data/trans_dic/IQ2608_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ2608_R3-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>75,19%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>90,35%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>78,53%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,38; 81,94</t>
+          <t>76,82; 88,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,27; 94,28</t>
+          <t>87,12; 95,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,69; 84,19</t>
+          <t>75,16; 86,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,05; 100,0</t>
+          <t>70,94; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,23; 88,87</t>
+          <t>66,84; 81,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,19; 95,13</t>
+          <t>85,7; 93,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,81; 86,91</t>
+          <t>71,55; 83,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>71,1; 100,0</t>
+          <t>68,26; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,28; 83,86</t>
+          <t>74,98; 83,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87,62; 93,67</t>
+          <t>87,52; 93,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,33; 84,56</t>
+          <t>76,24; 84,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,2; 97,74</t>
+          <t>78,63; 97,47</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>72,22%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>66,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>87,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>88,49%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71,48%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>86,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,79; 71,19</t>
+          <t>63,35; 72,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,7; 90,56</t>
+          <t>83,13; 90,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,6; 91,93</t>
+          <t>82,46; 89,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,97; 82,0</t>
+          <t>59,69; 83,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,01; 72,49</t>
+          <t>61,43; 71,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,27; 90,25</t>
+          <t>83,57; 90,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,73; 89,78</t>
+          <t>84,81; 91,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,28; 82,5</t>
+          <t>56,42; 79,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,12; 70,76</t>
+          <t>63,99; 70,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,38; 89,72</t>
+          <t>84,67; 89,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84,99; 89,79</t>
+          <t>84,76; 89,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,3; 79,02</t>
+          <t>62,48; 79,48</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62,15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69,01%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>47,87%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>77,34%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>79,26%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61,64%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,33%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,14; 55,01</t>
+          <t>55,39; 68,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,59; 82,86</t>
+          <t>67,68; 79,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,76; 83,81</t>
+          <t>75,12; 85,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,17; 75,33</t>
+          <t>56,91; 80,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,14; 68,44</t>
+          <t>40,36; 55,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,28; 79,76</t>
+          <t>71,8; 82,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,74; 84,93</t>
+          <t>73,69; 83,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,76; 79,84</t>
+          <t>45,92; 73,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,44; 60,47</t>
+          <t>50,88; 60,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71,56; 79,55</t>
+          <t>71,55; 79,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76,36; 82,96</t>
+          <t>76,29; 83,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55,97; 74,14</t>
+          <t>56,16; 73,71</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>74,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>82,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62,42%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>54,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>67,93%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>73,56%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>74,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,13; 59,72</t>
+          <t>43,4; 54,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,73; 73,42</t>
+          <t>69,59; 80,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,98; 78,84</t>
+          <t>76,71; 86,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,0; 67,98</t>
+          <t>52,32; 73,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,03; 54,01</t>
+          <t>48,55; 59,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,2; 79,63</t>
+          <t>62,27; 73,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,56; 86,66</t>
+          <t>67,51; 78,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,61; 73,33</t>
+          <t>45,95; 67,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,53; 55,14</t>
+          <t>47,36; 55,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,59; 75,2</t>
+          <t>67,66; 75,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,02; 81,37</t>
+          <t>74,04; 81,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,07; 67,48</t>
+          <t>51,4; 68,06</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>63,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>57,54; 63,48</t>
+          <t>60,47; 66,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,45; 83,3</t>
+          <t>79,41; 83,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,02; 82,81</t>
+          <t>80,85; 85,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58,15; 71,23</t>
+          <t>61,81; 74,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,82; 66,59</t>
+          <t>57,64; 63,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,33; 84,15</t>
+          <t>78,13; 83,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,0; 85,6</t>
+          <t>77,95; 82,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,76; 75,49</t>
+          <t>56,85; 70,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,12; 64,28</t>
+          <t>59,9; 64,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79,59; 83,12</t>
+          <t>79,62; 83,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80,28; 83,54</t>
+          <t>80,34; 83,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,92; 72,15</t>
+          <t>61,44; 70,9</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>88051</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>108596</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95642</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>67867</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>113563</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>94883</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12620</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88051</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>108596</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95642</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>21900</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60821; 73958</t>
+          <t>81390; 93555</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107172; 118499</t>
+          <t>103302; 112773</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86618; 101718</t>
+          <t>87675; 101459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9358; 13752</t>
+          <t>7921; 11166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81826; 94152</t>
+          <t>60328; 73816</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>103383; 112802</t>
+          <t>107712; 118069</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88439; 101377</t>
+          <t>86454; 100994</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10175; 14310</t>
+          <t>8689; 12729</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145740; 164544</t>
+          <t>147107; 164705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>214018; 228801</t>
+          <t>213777; 228140</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>181261; 200812</t>
+          <t>181053; 199522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23067; 27426</t>
+          <t>18788; 23291</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>297</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>172900</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>233612</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>223146</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28511</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>168419</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>206796</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>186282</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24546</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>172900</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>233612</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>223146</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32505</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57052</t>
+          <t>49812</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>156173; 179935</t>
+          <t>160761; 184110</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>197736; 213957</t>
+          <t>223612; 242690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178101; 193524</t>
+          <t>212797; 230746</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19906; 28159</t>
+          <t>23564; 32826</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>159901; 183960</t>
+          <t>155275; 180061</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>223998; 242771</t>
+          <t>197444; 214259</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>213498; 231676</t>
+          <t>178538; 192828</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26984; 36929</t>
+          <t>17263; 24431</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>324775; 358421</t>
+          <t>324127; 358306</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>426309; 453312</t>
+          <t>427812; 453149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>398227; 420743</t>
+          <t>397188; 420704</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50070; 62505</t>
+          <t>43784; 55701</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87956</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117204</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151487</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36778</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>61057</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>120988</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>149721</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24662</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>87956</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>117204</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>151487</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63194</t>
+          <t>59735</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52474; 70164</t>
+          <t>78388; 96840</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>111996; 129623</t>
+          <t>107315; 126509</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139329; 158324</t>
+          <t>141650; 160524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18872; 30139</t>
+          <t>30327; 42739</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78033; 96852</t>
+          <t>51478; 70360</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>108274; 126479</t>
+          <t>112325; 129325</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>140935; 160147</t>
+          <t>139204; 157472</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31740; 44642</t>
+          <t>17658; 28356</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135722; 162699</t>
+          <t>136886; 162493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>225418; 250589</t>
+          <t>225401; 251135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>288219; 313151</t>
+          <t>287963; 314072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53693; 71116</t>
+          <t>51523; 67631</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>100605</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>134807</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143521</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46458</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>105330</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>116384</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>127483</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31388</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100605</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>134807</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>143521</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48307</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79695</t>
+          <t>79616</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93427; 115920</t>
+          <t>89433; 112670</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>105763; 125799</t>
+          <t>125225; 144969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>117806; 136624</t>
+          <t>133516; 150996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25297; 37386</t>
+          <t>38941; 54606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88667; 111285</t>
+          <t>94236; 116035</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>124535; 143293</t>
+          <t>106692; 125378</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134984; 150822</t>
+          <t>116989; 136248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40395; 56304</t>
+          <t>26537; 39249</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190196; 220637</t>
+          <t>189504; 223095</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237449; 264183</t>
+          <t>237696; 266145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>257108; 282638</t>
+          <t>257178; 282762</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>68608; 88917</t>
+          <t>67946; 89967</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>801</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>146</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>449512</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>594219</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>449512</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>594219</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>382463; 421897</t>
+          <t>427713; 469268</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>541099; 574532</t>
+          <t>576562; 609777</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>541123; 574331</t>
+          <t>596134; 629014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83202; 101927</t>
+          <t>110250; 133410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>430161; 470967</t>
+          <t>383130; 422022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>575995; 611031</t>
+          <t>538893; 573373</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>597211; 631168</t>
+          <t>540588; 573493</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>120350; 144765</t>
+          <t>79324; 97910</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>824752; 881865</t>
+          <t>821846; 881029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1126863; 1176791</t>
+          <t>1127254; 1176340</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1148659; 1195316</t>
+          <t>1149605; 1195652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>210701; 241588</t>
+          <t>195323; 225383</t>
         </is>
       </c>
     </row>
